--- a/2607/emp_payroll_2607._populated.backup.xlsx
+++ b/2607/emp_payroll_2607._populated.backup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cheonghoongjun/onni/payroll-app/2607/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C0BA708-17FF-C740-980B-90DAA354A6C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E6B90FB-AFD3-904A-ABCA-89BEF1E9ED20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="jul27-reference" sheetId="1" r:id="rId1"/>
@@ -728,7 +728,9 @@
   <dimension ref="A1:X12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" bestFit="1" customWidth="1"/>
     <col min="11" max="20" width="9" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="12.6640625" bestFit="1" customWidth="1"/>
